--- a/docs/03_test/従業員一覧_テストケース.xlsx
+++ b/docs/03_test/従業員一覧_テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06CC7172-4CB6-4307-9BB8-D86FFDA9B5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2B06B1-63A5-4956-AA93-F5B6B23D52B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{18531DDC-B658-4C2C-B060-788A12619FEB}"/>
   </bookViews>
@@ -88,10 +88,14 @@
     <t>〇</t>
   </si>
   <si>
-    <t>従業員の一覧が表示される</t>
-  </si>
-  <si>
     <t>DBにある従業員がすべて表示される</t>
+  </si>
+  <si>
+    <t>一覧画面に従業員の一覧が表示される</t>
+    <rPh sb="0" eb="4">
+      <t>イチランガメン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -633,7 +637,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="4.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.4140625" customWidth="1"/>
+    <col min="3" max="3" width="33.58203125" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="6" max="6" width="23.1640625" customWidth="1"/>
   </cols>
@@ -656,7 +660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:6" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="3">
         <v>1</v>
       </c>
@@ -678,10 +682,10 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>7</v>
